--- a/league_registration_forms/040_neighborhood_tennis_doubles_tournament_entry_form--league_registration_forms.xlsx
+++ b/league_registration_forms/040_neighborhood_tennis_doubles_tournament_entry_form--league_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Match Preference</t>
+          <t>Team Member 2 Match Preference</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Match Date</t>
+          <t>Team Member 2 Match Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Match Time</t>
+          <t>Team Member 2 Match Time</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Team Member 2 Notes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Agreement</t>
+          <t>Team Member 2 Agreement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Team Venue</t>
+          <t>Team Member 2 Venue</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Team Score</t>
+          <t>Team Member 2 Score</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Team ELO</t>
+          <t>Team Member 2 Elo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Team UCLA</t>
+          <t>Team Member 2 Ucla</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'tennis_club'}</t>
+          <t>tennis_club</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Tennis Club'}</t>
+          <t>Tennis Club</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'home_court'}</t>
+          <t>home_court</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Home Court'}</t>
+          <t>Home Court</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'tennis_club'}</t>
+          <t>tennis_club</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Tennis Club'}</t>
+          <t>Tennis Club</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'home_court'}</t>
+          <t>home_court</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Home Court'}</t>
+          <t>Home Court</t>
         </is>
       </c>
     </row>
